--- a/실습파일/실습5_시험출제_풀코스.xlsx
+++ b/실습파일/실습5_시험출제_풀코스.xlsx
@@ -804,7 +804,7 @@
     <row r="23" ht="22" customHeight="1" s="23">
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [Gemini 실행] → [Gemini로 글과 파일(이미지, TXT, PDF, 음성 등) 행 단위 병렬 처리]</t>
+          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [Gemini 실행] → [Gemini로 글과 파일(이미지, TXT, PDF, 음성 등) 행 단위 병렬 처리]</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,13 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
+    <row r="35" ht="64" customHeight="1" s="23">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>참고 — [교사를 위한 올인원 도우미] 안의 [평가업무도우미] → [평가문항 만들기] 로도 같은 일을 할 수 있습니다. 설계 엑셀(내용 영역·배점·난이도·정답)을 그 창에서 새로 만들어 채우면 AI 가 문항을 자동 생성하고 시험지까지 이어 줍니다. 그 창의 [설정] 에 AI 키를 따로 넣어야 하고 요금이 들며, 결과는 선생님이 검토해야 합니다. 이 미션은 같은 원리를 엑셀 추가기능으로 직접 해 보는 것입니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="36" ht="24" customHeight="1" s="23">
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -917,7 +923,7 @@
     <row r="40" ht="22" customHeight="1" s="23">
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능] → [한글 파일 만들기]</t>
+          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능] → [한글 파일 만들기]</t>
         </is>
       </c>
     </row>
@@ -984,10 +990,10 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="32" customHeight="1" s="23">
+    <row r="50" ht="48" customHeight="1" s="23">
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>한글로 보내기 전에 미션 2에서 배운 [마크다운 문법 기호, 빈 줄 정리] 를 G열에 먼저 돌리세요. ** 와 ## 기호가 사라져 바로 쓸 수 있는 시험지 모양이 됩니다. 옵션은 1,2,4,6,11 을 권합니다.</t>
+          <t>순서는 하나만 고르세요. ① 위 4번 그대로 ## [문항 구성],**정답:** 으로 하면 ** 같은 마크다운 기호가 시험지에 남습니다. ② 기호 없이 하려면 미션 2의 [마크다운 문법 기호, 빈 줄 정리](옵션 1,2,4,6,11)를 G열에 먼저 돌린 뒤, 분할 문구를 기호 없이 [문항 구성],정답: 으로 적습니다(정답지는 정답: 하나).</t>
         </is>
       </c>
     </row>
@@ -1037,21 +1043,21 @@
     <row r="58" ht="22" customHeight="1" s="23">
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [Gemini 실행] → [Gemini로 이미지 행 단위 병렬 생성(Nano Banana)]</t>
+          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [Gemini 실행] → [Gemini로 이미지 행 단위 병렬 생성(Nano Banana)]</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" s="23">
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3.  '[설정 0/8] 모델 선택' → 1   (기본 권장 gemini-3.1-flash-image)</t>
+          <t>3.  '[설정 0/8] 모델 선택' → 1   (기본 권장 gemini-nano-banana-2.1)</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" s="23">
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>4.  '[설정 1/8] 해상도' → 1   (1K, 이미지당 약 $0.067)</t>
+          <t>4.  '[설정 1/8] 해상도' → 1   (1K, 이미지당 약 $0.044)</t>
         </is>
       </c>
     </row>
@@ -1125,10 +1131,10 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="32" customHeight="1" s="23">
+    <row r="71" ht="48" customHeight="1" s="23">
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>비용 주의 : 범위에 잡은 행은 모두 그림을 만듭니다. 문항 안에 '없음' 이라고 적혀 있어도 그 행까지 만듭니다. 15행을 잡으면 15장이 만들어지고 1K 기준 약 1,400원입니다.</t>
+          <t>비용 주의 : 범위에 잡은 행은 모두 그림을 만듭니다. 문항 안에 '없음' 이라고 적혀 있어도 그 행까지 만듭니다. 15행을 잡으면 15장이 만들어지고 1K 기준 약 900원 남짓(장당 약 $0.044)입니다.</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2632,7 @@
     <row r="17" ht="22" customHeight="1" s="23">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능] → [한글 파일 만들기]</t>
+          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능] → [한글 파일 만들기]</t>
         </is>
       </c>
     </row>
@@ -2728,10 +2734,10 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1" s="23">
+    <row r="34" ht="48" customHeight="1" s="23">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>다만 마크다운을 지우면 분할 기준도 함께 바뀝니다. ** 를 지웠으면 분할 문구를   [문항 구성],정답:  처럼 기호 없는 형태로 적어야 합니다. 정리를 먼저 할지 나중에 할지 정해 두고 그에 맞춰 기준을 적으세요.</t>
+          <t>다만 마크다운을 지우면 분할 기준도 함께 바뀝니다. ** 를 지웠으면 분할 문구를   [문항 구성],정답:  처럼 기호 없는 형태로 적어야 합니다. 정리를 했으면 기호 없는 기준을, 하지 않았으면 위 4번의 ## [문항 구성],**정답:** 을 적으세요. 둘을 섞지 마세요.</t>
         </is>
       </c>
     </row>
